--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9399,0.0116,0.0101,0.0038</t>
-  </si>
-  <si>
-    <t>0.0260,0.0004,0.0002,0.9933</t>
-  </si>
-  <si>
-    <t>0.9848,0.0012,0.0017,0.0017</t>
-  </si>
-  <si>
-    <t>0.0106,0.0003,0.0003,0.9966</t>
-  </si>
-  <si>
-    <t>0.9979,0.0005,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9971,0.0005,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9974,0.0006,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9971,0.0005,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9960,0.0011,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9917,0.0023,0.0003,0.0018</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.8865,0.0023,0.1066,0.0005</t>
-  </si>
-  <si>
-    <t>0.5313,0.0011,0.5673,0.0006</t>
-  </si>
-  <si>
-    <t>0.9168,0.0038,0.0571,0.0002</t>
-  </si>
-  <si>
-    <t>0.2328,0.0023,0.8001,0.0022</t>
-  </si>
-  <si>
-    <t>0.9117,0.0071,0.0502,0.0008</t>
-  </si>
-  <si>
-    <t>0.0004,0.9984,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.9940,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.0763,0.9087,0.0056,0.0026</t>
-  </si>
-  <si>
-    <t>0.0142,0.9833,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9015,0.0006,0.1004,0.0005</t>
-  </si>
-  <si>
-    <t>0.8923,0.0010,0.1105,0.0004</t>
-  </si>
-  <si>
-    <t>0.3867,0.0012,0.6992,0.0007</t>
-  </si>
-  <si>
-    <t>0.6722,0.0007,0.4332,0.0002</t>
-  </si>
-  <si>
-    <t>0.1947,0.0003,0.8693,0.0003</t>
-  </si>
-  <si>
-    <t>0.7565,0.0004,0.2955,0.0007</t>
-  </si>
-  <si>
-    <t>0.0187,0.0001,0.9828,0.0005</t>
-  </si>
-  <si>
-    <t>0.8144,0.1827,0.0096,0.0009</t>
-  </si>
-  <si>
-    <t>0.9580,0.0100,0.0075,0.0010</t>
-  </si>
-  <si>
-    <t>0.0010,0.0008,0.9987,0.0007</t>
-  </si>
-  <si>
-    <t>0.0556,0.8659,0.0966,0.0026</t>
-  </si>
-  <si>
-    <t>0.9812,0.0054,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.9274,0.0145,0.0322,0.0016</t>
-  </si>
-  <si>
-    <t>0.8614,0.1670,0.0046,0.0010</t>
-  </si>
-  <si>
-    <t>0.0465,0.8813,0.1234,0.0009</t>
-  </si>
-  <si>
-    <t>0.0586,0.0252,0.4096,0.4138</t>
-  </si>
-  <si>
-    <t>0.6928,0.0014,0.2367,0.0128</t>
-  </si>
-  <si>
-    <t>0.4543,0.0008,0.5355,0.0053</t>
-  </si>
-  <si>
-    <t>0.8059,0.0006,0.2348,0.0006</t>
-  </si>
-  <si>
-    <t>0.5438,0.0020,0.5305,0.0011</t>
-  </si>
-  <si>
-    <t>0.0196,0.9543,0.0340,0.0013</t>
-  </si>
-  <si>
-    <t>0.1017,0.0008,0.7914,0.0312</t>
-  </si>
-  <si>
-    <t>0.0013,0.0158,0.0000,0.9988</t>
-  </si>
-  <si>
-    <t>0.0020,0.9918,0.0040,0.0022</t>
-  </si>
-  <si>
-    <t>0.0119,0.9723,0.0235,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.9988,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.1608,0.0017,0.8564,0.0018</t>
-  </si>
-  <si>
-    <t>0.0813,0.0155,0.8872,0.0019</t>
-  </si>
-  <si>
-    <t>0.5514,0.0007,0.5522,0.0005</t>
-  </si>
-  <si>
-    <t>0.2782,0.0003,0.8196,0.0002</t>
-  </si>
-  <si>
-    <t>0.0133,0.0003,0.9887,0.0004</t>
-  </si>
-  <si>
-    <t>0.2492,0.0025,0.8000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9923,0.0019,0.0004,0.0014</t>
-  </si>
-  <si>
-    <t>0.9940,0.0013,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.9926,0.0026,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.0064,0.0069,0.9869,0.0239</t>
-  </si>
-  <si>
-    <t>0.9960,0.0006,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9936,0.0023,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9865,0.0066,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.0168,0.3957,0.7783,0.0037</t>
-  </si>
-  <si>
-    <t>0.0440,0.0005,0.9552,0.0012</t>
-  </si>
-  <si>
-    <t>0.4800,0.0009,0.5251,0.0052</t>
-  </si>
-  <si>
-    <t>0.0054,0.4792,0.9068,0.0014</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9963,0.0024</t>
-  </si>
-  <si>
-    <t>0.0352,0.9495,0.0171,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9266,0.0029,0.0561,0.0003</t>
-  </si>
-  <si>
-    <t>0.7465,0.0140,0.2148,0.0013</t>
-  </si>
-  <si>
-    <t>0.0072,0.0022,0.9918,0.0041</t>
-  </si>
-  <si>
-    <t>0.0191,0.5276,0.6475,0.0022</t>
-  </si>
-  <si>
-    <t>0.0983,0.1296,0.7349,0.0018</t>
-  </si>
-  <si>
-    <t>0.0169,0.9312,0.0847,0.0062</t>
-  </si>
-  <si>
-    <t>0.0268,0.6961,0.4011,0.0020</t>
-  </si>
-  <si>
-    <t>0.0353,0.0006,0.0096,0.9607</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0027,0.0004,0.0001,0.9993</t>
-  </si>
-  <si>
-    <t>0.0031,0.0004,0.0001,0.9990</t>
-  </si>
-  <si>
-    <t>0.0121,0.0002,0.0011,0.9936</t>
-  </si>
-  <si>
-    <t>0.0015,0.0003,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.0487,0.4548,0.5051,0.0401</t>
-  </si>
-  <si>
-    <t>0.0963,0.1187,0.7505,0.0017</t>
-  </si>
-  <si>
-    <t>0.0798,0.2644,0.5916,0.0054</t>
-  </si>
-  <si>
-    <t>0.3082,0.0073,0.6979,0.0068</t>
-  </si>
-  <si>
-    <t>0.2192,0.1041,0.5631,0.0035</t>
-  </si>
-  <si>
-    <t>0.0568,0.1305,0.7956,0.0039</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9959,0.0012,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9906,0.0034,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9960,0.0011,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9912,0.0030,0.0004,0.0017</t>
-  </si>
-  <si>
-    <t>0.9950,0.0013,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.9930,0.0029,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9921,0.0041,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9976,0.0007,0.0001,0.0003</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9625,0.0033,0.0034,0.0040</t>
+  </si>
+  <si>
+    <t>0.0756,0.0006,0.0006,0.9731</t>
+  </si>
+  <si>
+    <t>0.9220,0.0018,0.0017,0.0370</t>
+  </si>
+  <si>
+    <t>0.0321,0.0006,0.0002,0.9915</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9956,0.0010,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9962,0.0007,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9968,0.0008,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9958,0.0014,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9925,0.0022,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9522,0.0027,0.0205,0.0004</t>
+  </si>
+  <si>
+    <t>0.5147,0.0023,0.5431,0.0013</t>
+  </si>
+  <si>
+    <t>0.8171,0.0053,0.1845,0.0016</t>
+  </si>
+  <si>
+    <t>0.0716,0.0016,0.9349,0.0014</t>
+  </si>
+  <si>
+    <t>0.8832,0.0045,0.0687,0.0046</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.9931,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.1606,0.8389,0.0095,0.0031</t>
+  </si>
+  <si>
+    <t>0.0153,0.9801,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.8639,0.0011,0.1376,0.0011</t>
+  </si>
+  <si>
+    <t>0.8652,0.0007,0.1620,0.0002</t>
+  </si>
+  <si>
+    <t>0.1939,0.0007,0.8173,0.0045</t>
+  </si>
+  <si>
+    <t>0.3307,0.0012,0.7472,0.0007</t>
+  </si>
+  <si>
+    <t>0.6558,0.0004,0.4612,0.0003</t>
+  </si>
+  <si>
+    <t>0.5671,0.0003,0.5209,0.0007</t>
+  </si>
+  <si>
+    <t>0.0446,0.0002,0.9600,0.0009</t>
+  </si>
+  <si>
+    <t>0.7544,0.2131,0.0192,0.0024</t>
+  </si>
+  <si>
+    <t>0.9523,0.0064,0.0082,0.0037</t>
+  </si>
+  <si>
+    <t>0.0021,0.0008,0.9975,0.0014</t>
+  </si>
+  <si>
+    <t>0.0304,0.9517,0.0193,0.0007</t>
+  </si>
+  <si>
+    <t>0.9865,0.0030,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.7374,0.0077,0.2361,0.0025</t>
+  </si>
+  <si>
+    <t>0.7771,0.2674,0.0052,0.0009</t>
+  </si>
+  <si>
+    <t>0.0795,0.7716,0.2088,0.0027</t>
+  </si>
+  <si>
+    <t>0.0716,0.0278,0.8585,0.0136</t>
+  </si>
+  <si>
+    <t>0.8357,0.0011,0.1220,0.0048</t>
+  </si>
+  <si>
+    <t>0.3609,0.0005,0.5562,0.0104</t>
+  </si>
+  <si>
+    <t>0.5364,0.0004,0.5530,0.0008</t>
+  </si>
+  <si>
+    <t>0.6923,0.0023,0.3585,0.0014</t>
+  </si>
+  <si>
+    <t>0.0616,0.7802,0.1538,0.0060</t>
+  </si>
+  <si>
+    <t>0.1882,0.0006,0.5861,0.0444</t>
+  </si>
+  <si>
+    <t>0.0029,0.0094,0.0001,0.9982</t>
+  </si>
+  <si>
+    <t>0.0005,0.9980,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9932,0.0045,0.0037</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0207,0.0066,0.9623,0.0018</t>
+  </si>
+  <si>
+    <t>0.0872,0.0185,0.8795,0.0008</t>
+  </si>
+  <si>
+    <t>0.5490,0.0003,0.5670,0.0003</t>
+  </si>
+  <si>
+    <t>0.1927,0.0004,0.8712,0.0003</t>
+  </si>
+  <si>
+    <t>0.0446,0.0002,0.9628,0.0005</t>
+  </si>
+  <si>
+    <t>0.1178,0.0011,0.9037,0.0007</t>
+  </si>
+  <si>
+    <t>0.9785,0.0086,0.0013,0.0026</t>
+  </si>
+  <si>
+    <t>0.9920,0.0019,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9957,0.0016,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0278,0.0034,0.9397,0.0660</t>
+  </si>
+  <si>
+    <t>0.9950,0.0011,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9944,0.0015,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9885,0.0040,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.0169,0.4035,0.7838,0.0048</t>
+  </si>
+  <si>
+    <t>0.0242,0.0008,0.9671,0.0024</t>
+  </si>
+  <si>
+    <t>0.2171,0.0008,0.7765,0.0047</t>
+  </si>
+  <si>
+    <t>0.0085,0.1944,0.9467,0.0012</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9964,0.0021</t>
+  </si>
+  <si>
+    <t>0.0034,0.9928,0.0048,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9991,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.6527,0.0031,0.3987,0.0009</t>
+  </si>
+  <si>
+    <t>0.7721,0.0236,0.1574,0.0015</t>
+  </si>
+  <si>
+    <t>0.0213,0.0018,0.9802,0.0045</t>
+  </si>
+  <si>
+    <t>0.0092,0.7020,0.6998,0.0030</t>
+  </si>
+  <si>
+    <t>0.1935,0.0308,0.7471,0.0017</t>
+  </si>
+  <si>
+    <t>0.0076,0.9704,0.0483,0.0033</t>
+  </si>
+  <si>
+    <t>0.0652,0.1145,0.7885,0.0015</t>
+  </si>
+  <si>
+    <t>0.0024,0.0003,0.0023,0.9975</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0081,0.0010,0.0003,0.9972</t>
+  </si>
+  <si>
+    <t>0.0008,0.0004,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0489,0.0007,0.0008,0.9793</t>
+  </si>
+  <si>
+    <t>0.0014,0.0003,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0165,0.8289,0.3383,0.0116</t>
+  </si>
+  <si>
+    <t>0.0129,0.3691,0.8786,0.0007</t>
+  </si>
+  <si>
+    <t>0.1640,0.0029,0.8661,0.0006</t>
+  </si>
+  <si>
+    <t>0.1210,0.0607,0.7216,0.0286</t>
+  </si>
+  <si>
+    <t>0.1019,0.1701,0.6653,0.0035</t>
+  </si>
+  <si>
+    <t>0.0870,0.2182,0.6004,0.0084</t>
+  </si>
+  <si>
+    <t>0.9943,0.0008,0.0002,0.0024</t>
+  </si>
+  <si>
+    <t>0.9942,0.0018,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9936,0.0011,0.0002,0.0019</t>
+  </si>
+  <si>
+    <t>0.9938,0.0019,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9865,0.0051,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9915,0.0031,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9950,0.0018,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9889,0.0062,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9964,0.0008,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9964,0.0004,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9942,0.0019,0.0003,0.0010</t>
   </si>
   <si>
     <t>0.9971,0.0006,0.0001,0.0007</t>
   </si>
   <si>
-    <t>0.9967,0.0005,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9958,0.0010,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9964,0.0005,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9888,0.0047,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.9968,0.0007,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0150,0.0002,0.9874,0.0005</t>
-  </si>
-  <si>
-    <t>0.2901,0.0005,0.7938,0.0005</t>
-  </si>
-  <si>
-    <t>0.9630,0.0015,0.0165,0.0001</t>
-  </si>
-  <si>
-    <t>0.3002,0.0013,0.7544,0.0016</t>
-  </si>
-  <si>
-    <t>0.0034,0.9915,0.0031,0.0006</t>
-  </si>
-  <si>
-    <t>0.0009,0.9959,0.0116,0.0000</t>
-  </si>
-  <si>
-    <t>0.0635,0.8888,0.0045,0.0075</t>
-  </si>
-  <si>
-    <t>0.0067,0.9877,0.0041,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9987,0.0045,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.4648,0.5768,0.0105,0.0018</t>
-  </si>
-  <si>
-    <t>0.9110,0.0078,0.0483,0.0015</t>
-  </si>
-  <si>
-    <t>0.4995,0.0016,0.5624,0.0017</t>
-  </si>
-  <si>
-    <t>0.9291,0.0025,0.0218,0.0042</t>
-  </si>
-  <si>
-    <t>0.5098,0.0055,0.5359,0.0016</t>
-  </si>
-  <si>
-    <t>0.0021,0.0013,0.0003,0.9988</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.9926,0.0040,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.9752,0.4447,0.0003</t>
-  </si>
-  <si>
-    <t>0.0030,0.9914,0.0111,0.0000</t>
-  </si>
-  <si>
-    <t>0.7774,0.1820,0.0096,0.0081</t>
-  </si>
-  <si>
-    <t>0.3508,0.6411,0.0106,0.0031</t>
-  </si>
-  <si>
-    <t>0.9936,0.0015,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9910,0.0009,0.0002,0.0033</t>
-  </si>
-  <si>
-    <t>0.9944,0.0010,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9953,0.0008,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9941,0.0004,0.0001,0.0031</t>
-  </si>
-  <si>
-    <t>0.9947,0.0018,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9899,0.0003,0.0001,0.0077</t>
-  </si>
-  <si>
-    <t>0.9981,0.0004,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.1563,0.0163,0.8077,0.0055</t>
-  </si>
-  <si>
-    <t>0.1080,0.0291,0.8479,0.0026</t>
-  </si>
-  <si>
-    <t>0.1593,0.0009,0.8628,0.0016</t>
-  </si>
-  <si>
-    <t>0.3089,0.0026,0.7578,0.0007</t>
-  </si>
-  <si>
-    <t>0.9301,0.0042,0.0406,0.0006</t>
-  </si>
-  <si>
-    <t>0.8878,0.0048,0.0844,0.0014</t>
-  </si>
-  <si>
-    <t>0.5991,0.0006,0.4795,0.0010</t>
-  </si>
-  <si>
-    <t>0.9018,0.0229,0.0233,0.0018</t>
-  </si>
-  <si>
-    <t>0.0057,0.0003,0.0001,0.9984</t>
+    <t>0.9972,0.0005,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.0055,0.0002,0.9951,0.0003</t>
+  </si>
+  <si>
+    <t>0.4903,0.0017,0.6081,0.0003</t>
+  </si>
+  <si>
+    <t>0.9678,0.0012,0.0134,0.0001</t>
+  </si>
+  <si>
+    <t>0.0594,0.0006,0.9565,0.0003</t>
+  </si>
+  <si>
+    <t>0.0088,0.9857,0.0046,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9975,0.0090,0.0000</t>
+  </si>
+  <si>
+    <t>0.0243,0.9504,0.0068,0.0032</t>
+  </si>
+  <si>
+    <t>0.0186,0.9756,0.0036,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.9979,0.0064,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9989,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.4334,0.6330,0.0072,0.0011</t>
+  </si>
+  <si>
+    <t>0.8424,0.0045,0.1409,0.0020</t>
+  </si>
+  <si>
+    <t>0.7971,0.0011,0.2564,0.0004</t>
+  </si>
+  <si>
+    <t>0.9365,0.0023,0.0262,0.0021</t>
+  </si>
+  <si>
+    <t>0.8574,0.0019,0.1409,0.0012</t>
+  </si>
+  <si>
+    <t>0.0040,0.0039,0.0003,0.9979</t>
+  </si>
+  <si>
+    <t>0.0002,0.9991,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0035,0.9918,0.0066,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.9717,0.4797,0.0003</t>
+  </si>
+  <si>
+    <t>0.0075,0.9848,0.0105,0.0001</t>
+  </si>
+  <si>
+    <t>0.8442,0.1081,0.0243,0.0055</t>
+  </si>
+  <si>
+    <t>0.8738,0.0964,0.0061,0.0051</t>
+  </si>
+  <si>
+    <t>0.9937,0.0016,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9925,0.0007,0.0002,0.0029</t>
+  </si>
+  <si>
+    <t>0.9955,0.0005,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9940,0.0010,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9945,0.0003,0.0001,0.0029</t>
+  </si>
+  <si>
+    <t>0.9950,0.0014,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9945,0.0006,0.0002,0.0024</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.1032,0.0197,0.8092,0.0279</t>
+  </si>
+  <si>
+    <t>0.1660,0.0171,0.8089,0.0018</t>
+  </si>
+  <si>
+    <t>0.3621,0.0016,0.7016,0.0011</t>
+  </si>
+  <si>
+    <t>0.4205,0.0016,0.6553,0.0011</t>
+  </si>
+  <si>
+    <t>0.9822,0.0015,0.0034,0.0001</t>
+  </si>
+  <si>
+    <t>0.9484,0.0023,0.0248,0.0007</t>
+  </si>
+  <si>
+    <t>0.6948,0.0008,0.4004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9433,0.0025,0.0292,0.0005</t>
+  </si>
+  <si>
+    <t>0.0523,0.0006,0.0002,0.9846</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0013,0.0002,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.0132,0.0002,0.0008,0.9937</t>
-  </si>
-  <si>
-    <t>0.0278,0.3370,0.7336,0.0025</t>
-  </si>
-  <si>
-    <t>0.9971,0.0005,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.3009,0.7136,0.0059,0.0044</t>
-  </si>
-  <si>
-    <t>0.9929,0.0009,0.0005,0.0014</t>
-  </si>
-  <si>
-    <t>0.5511,0.4138,0.0164,0.0071</t>
-  </si>
-  <si>
-    <t>0.9933,0.0013,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.8415,0.0016,0.0012,0.1466</t>
-  </si>
-  <si>
-    <t>0.9957,0.0008,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.0574,0.0312,0.9145,0.0045</t>
-  </si>
-  <si>
-    <t>0.9819,0.0016,0.0020,0.0037</t>
-  </si>
-  <si>
-    <t>0.9898,0.0012,0.0007,0.0031</t>
-  </si>
-  <si>
-    <t>0.8744,0.0747,0.0134,0.0018</t>
-  </si>
-  <si>
-    <t>0.9865,0.0029,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.9707,0.0078,0.0042,0.0015</t>
-  </si>
-  <si>
-    <t>0.7293,0.1503,0.0418,0.0063</t>
-  </si>
-  <si>
-    <t>0.9161,0.0060,0.0483,0.0004</t>
-  </si>
-  <si>
-    <t>0.9806,0.0041,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.9962,0.0004,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9976,0.0005,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9965,0.0006,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9965,0.0005,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9962,0.0007,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9955,0.0006,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9974,0.0005,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.8650,0.1314,0.0031,0.0025</t>
-  </si>
-  <si>
-    <t>0.7368,0.2957,0.0127,0.0016</t>
-  </si>
-  <si>
-    <t>0.2508,0.7685,0.0149,0.0013</t>
-  </si>
-  <si>
-    <t>0.9423,0.0184,0.0079,0.0101</t>
-  </si>
-  <si>
-    <t>0.9800,0.0123,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.9884,0.0029,0.0009,0.0013</t>
-  </si>
-  <si>
-    <t>0.9884,0.0048,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9609,0.0242,0.0020,0.0024</t>
-  </si>
-  <si>
-    <t>0.0063,0.0060,0.9939,0.0005</t>
-  </si>
-  <si>
-    <t>0.9681,0.0096,0.0029,0.0056</t>
-  </si>
-  <si>
-    <t>0.0907,0.0004,0.9350,0.0003</t>
-  </si>
-  <si>
-    <t>0.1116,0.0313,0.8348,0.0008</t>
-  </si>
-  <si>
-    <t>0.4384,0.0010,0.6774,0.0004</t>
-  </si>
-  <si>
-    <t>0.1135,0.0021,0.8997,0.0013</t>
-  </si>
-  <si>
-    <t>0.2316,0.0007,0.8384,0.0003</t>
-  </si>
-  <si>
-    <t>0.0123,0.0001,0.9880,0.0005</t>
-  </si>
-  <si>
-    <t>0.1086,0.0004,0.9233,0.0004</t>
-  </si>
-  <si>
-    <t>0.8044,0.0025,0.2143,0.0011</t>
-  </si>
-  <si>
-    <t>0.6986,0.0012,0.3773,0.0005</t>
-  </si>
-  <si>
-    <t>0.9168,0.0057,0.0429,0.0014</t>
-  </si>
-  <si>
-    <t>0.5548,0.0094,0.4720,0.0015</t>
-  </si>
-  <si>
-    <t>0.6654,0.0369,0.2918,0.0023</t>
-  </si>
-  <si>
-    <t>0.7580,0.0105,0.2371,0.0010</t>
-  </si>
-  <si>
-    <t>0.8334,0.0054,0.1501,0.0017</t>
-  </si>
-  <si>
-    <t>0.8898,0.0099,0.0600,0.0029</t>
-  </si>
-  <si>
-    <t>0.6093,0.4385,0.0062,0.0021</t>
-  </si>
-  <si>
-    <t>0.0295,0.9594,0.0089,0.0007</t>
-  </si>
-  <si>
-    <t>0.8562,0.1763,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.8398,0.2057,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.3415,0.6708,0.0044,0.0022</t>
-  </si>
-  <si>
-    <t>0.9243,0.0077,0.0310,0.0008</t>
-  </si>
-  <si>
-    <t>0.9472,0.0016,0.0316,0.0002</t>
-  </si>
-  <si>
-    <t>0.9578,0.0009,0.0126,0.0015</t>
-  </si>
-  <si>
-    <t>0.6987,0.0063,0.3308,0.0013</t>
-  </si>
-  <si>
-    <t>0.9109,0.0010,0.0743,0.0011</t>
-  </si>
-  <si>
-    <t>0.2120,0.0005,0.8513,0.0003</t>
-  </si>
-  <si>
-    <t>0.4836,0.0012,0.5016,0.0072</t>
-  </si>
-  <si>
-    <t>0.8185,0.0008,0.2138,0.0007</t>
-  </si>
-  <si>
-    <t>0.7084,0.0003,0.3698,0.0005</t>
-  </si>
-  <si>
-    <t>0.3325,0.0254,0.5928,0.0196</t>
-  </si>
-  <si>
-    <t>0.9954,0.0006,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.9839,0.0039,0.0007,0.0044</t>
-  </si>
-  <si>
-    <t>0.9818,0.0042,0.0007,0.0053</t>
-  </si>
-  <si>
-    <t>0.9952,0.0015,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9831,0.0065,0.0007,0.0028</t>
-  </si>
-  <si>
-    <t>0.9938,0.0019,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9973,0.0005,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9963,0.0006,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.0941,0.0966,0.8231,0.0045</t>
-  </si>
-  <si>
-    <t>0.6768,0.2024,0.0381,0.0152</t>
-  </si>
-  <si>
-    <t>0.8815,0.0015,0.0055,0.0687</t>
-  </si>
-  <si>
-    <t>0.2099,0.0002,0.8533,0.0003</t>
-  </si>
-  <si>
-    <t>0.0034,0.0002,0.9904,0.0047</t>
-  </si>
-  <si>
-    <t>0.1261,0.0101,0.8567,0.0019</t>
-  </si>
-  <si>
-    <t>0.0187,0.0002,0.9826,0.0004</t>
-  </si>
-  <si>
-    <t>0.3532,0.0009,0.7317,0.0006</t>
-  </si>
-  <si>
-    <t>0.0100,0.0002,0.9862,0.0009</t>
-  </si>
-  <si>
-    <t>0.2676,0.0016,0.7949,0.0005</t>
-  </si>
-  <si>
-    <t>0.2850,0.0013,0.7068,0.0083</t>
-  </si>
-  <si>
-    <t>0.9316,0.0028,0.0407,0.0012</t>
-  </si>
-  <si>
-    <t>0.9536,0.0011,0.0282,0.0003</t>
-  </si>
-  <si>
-    <t>0.9804,0.0007,0.0059,0.0002</t>
-  </si>
-  <si>
-    <t>0.9747,0.0235,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9944,0.0016,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9962,0.0009,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9838,0.0098,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9941,0.0015,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9802,0.0129,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.9917,0.0020,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.9903,0.0052,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.5990,0.0010,0.4918,0.0005</t>
-  </si>
-  <si>
-    <t>0.0280,0.0004,0.9741,0.0005</t>
-  </si>
-  <si>
-    <t>0.4619,0.0023,0.6035,0.0020</t>
-  </si>
-  <si>
-    <t>0.6592,0.0054,0.3743,0.0017</t>
-  </si>
-  <si>
-    <t>0.5412,0.0002,0.5793,0.0003</t>
-  </si>
-  <si>
-    <t>0.8070,0.0005,0.0953,0.0100</t>
-  </si>
-  <si>
-    <t>0.8711,0.0005,0.1493,0.0003</t>
-  </si>
-  <si>
-    <t>0.8051,0.0006,0.1951,0.0018</t>
-  </si>
-  <si>
-    <t>0.9221,0.0011,0.0013,0.0568</t>
-  </si>
-  <si>
-    <t>0.3552,0.0021,0.0072,0.6005</t>
-  </si>
-  <si>
-    <t>0.1078,0.0005,0.0003,0.9652</t>
+    <t>0.0006,0.0002,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0251,0.0002,0.0005,0.9903</t>
+  </si>
+  <si>
+    <t>0.0333,0.1821,0.8250,0.0033</t>
+  </si>
+  <si>
+    <t>0.9966,0.0008,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.3130,0.7065,0.0101,0.0031</t>
+  </si>
+  <si>
+    <t>0.9954,0.0006,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.7107,0.2854,0.0141,0.0035</t>
+  </si>
+  <si>
+    <t>0.9872,0.0012,0.0009,0.0047</t>
+  </si>
+  <si>
+    <t>0.9326,0.0019,0.0018,0.0350</t>
+  </si>
+  <si>
+    <t>0.9949,0.0009,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.0508,0.0153,0.9301,0.0069</t>
+  </si>
+  <si>
+    <t>0.9870,0.0022,0.0012,0.0015</t>
+  </si>
+  <si>
+    <t>0.9853,0.0040,0.0010,0.0026</t>
+  </si>
+  <si>
+    <t>0.2989,0.7086,0.0126,0.0036</t>
+  </si>
+  <si>
+    <t>0.9899,0.0019,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9504,0.0176,0.0078,0.0009</t>
+  </si>
+  <si>
+    <t>0.7452,0.1488,0.0276,0.0060</t>
+  </si>
+  <si>
+    <t>0.8674,0.0243,0.0631,0.0010</t>
+  </si>
+  <si>
+    <t>0.9628,0.0103,0.0054,0.0011</t>
+  </si>
+  <si>
+    <t>0.9952,0.0005,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9975,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9965,0.0007,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9944,0.0013,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9891,0.0011,0.0004,0.0052</t>
+  </si>
+  <si>
+    <t>0.9949,0.0008,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9224,0.0679,0.0027,0.0015</t>
+  </si>
+  <si>
+    <t>0.8556,0.1652,0.0064,0.0016</t>
+  </si>
+  <si>
+    <t>0.5883,0.4276,0.0131,0.0030</t>
+  </si>
+  <si>
+    <t>0.9591,0.0231,0.0022,0.0020</t>
+  </si>
+  <si>
+    <t>0.9665,0.0231,0.0014,0.0023</t>
+  </si>
+  <si>
+    <t>0.9935,0.0018,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9775,0.0126,0.0017,0.0014</t>
+  </si>
+  <si>
+    <t>0.9553,0.0262,0.0025,0.0033</t>
+  </si>
+  <si>
+    <t>0.0015,0.0033,0.9983,0.0004</t>
+  </si>
+  <si>
+    <t>0.9585,0.0096,0.0040,0.0109</t>
+  </si>
+  <si>
+    <t>0.0184,0.0003,0.9832,0.0004</t>
+  </si>
+  <si>
+    <t>0.2420,0.0019,0.8083,0.0007</t>
+  </si>
+  <si>
+    <t>0.3283,0.0004,0.7826,0.0002</t>
+  </si>
+  <si>
+    <t>0.1171,0.0053,0.8860,0.0019</t>
+  </si>
+  <si>
+    <t>0.4038,0.0007,0.7092,0.0003</t>
+  </si>
+  <si>
+    <t>0.0061,0.0002,0.9923,0.0006</t>
+  </si>
+  <si>
+    <t>0.0686,0.0004,0.9513,0.0003</t>
+  </si>
+  <si>
+    <t>0.5553,0.0028,0.5062,0.0014</t>
+  </si>
+  <si>
+    <t>0.8474,0.0021,0.1615,0.0006</t>
+  </si>
+  <si>
+    <t>0.8941,0.0031,0.0798,0.0017</t>
+  </si>
+  <si>
+    <t>0.8775,0.0298,0.0473,0.0017</t>
+  </si>
+  <si>
+    <t>0.5874,0.0588,0.3176,0.0036</t>
+  </si>
+  <si>
+    <t>0.7971,0.0019,0.2459,0.0002</t>
+  </si>
+  <si>
+    <t>0.9289,0.0025,0.0394,0.0014</t>
+  </si>
+  <si>
+    <t>0.8728,0.0088,0.0739,0.0048</t>
+  </si>
+  <si>
+    <t>0.7260,0.3103,0.0037,0.0021</t>
+  </si>
+  <si>
+    <t>0.0778,0.9030,0.0169,0.0022</t>
+  </si>
+  <si>
+    <t>0.5983,0.4339,0.0052,0.0016</t>
+  </si>
+  <si>
+    <t>0.8393,0.1892,0.0019,0.0015</t>
+  </si>
+  <si>
+    <t>0.6541,0.3953,0.0036,0.0013</t>
+  </si>
+  <si>
+    <t>0.9119,0.0150,0.0239,0.0021</t>
+  </si>
+  <si>
+    <t>0.9731,0.0011,0.0096,0.0003</t>
+  </si>
+  <si>
+    <t>0.9655,0.0013,0.0071,0.0016</t>
+  </si>
+  <si>
+    <t>0.7476,0.0038,0.2804,0.0009</t>
+  </si>
+  <si>
+    <t>0.9473,0.0009,0.0332,0.0007</t>
+  </si>
+  <si>
+    <t>0.0867,0.0004,0.9384,0.0003</t>
+  </si>
+  <si>
+    <t>0.8366,0.0014,0.1020,0.0073</t>
+  </si>
+  <si>
+    <t>0.8080,0.0009,0.2387,0.0004</t>
+  </si>
+  <si>
+    <t>0.7397,0.0006,0.3388,0.0004</t>
+  </si>
+  <si>
+    <t>0.4932,0.0028,0.5346,0.0054</t>
+  </si>
+  <si>
+    <t>0.9926,0.0008,0.0001,0.0034</t>
+  </si>
+  <si>
+    <t>0.9934,0.0016,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9838,0.0046,0.0006,0.0041</t>
+  </si>
+  <si>
+    <t>0.9967,0.0011,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9887,0.0027,0.0005,0.0029</t>
+  </si>
+  <si>
+    <t>0.9917,0.0028,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9917,0.0016,0.0003,0.0027</t>
+  </si>
+  <si>
+    <t>0.9968,0.0005,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.1874,0.1027,0.6855,0.0033</t>
+  </si>
+  <si>
+    <t>0.1828,0.7305,0.0819,0.0057</t>
+  </si>
+  <si>
+    <t>0.9651,0.0038,0.0041,0.0087</t>
+  </si>
+  <si>
+    <t>0.1016,0.0001,0.9293,0.0002</t>
+  </si>
+  <si>
+    <t>0.0057,0.0004,0.9878,0.0030</t>
+  </si>
+  <si>
+    <t>0.0732,0.3253,0.5967,0.0028</t>
+  </si>
+  <si>
+    <t>0.0273,0.0002,0.9761,0.0004</t>
+  </si>
+  <si>
+    <t>0.5542,0.0008,0.5259,0.0010</t>
+  </si>
+  <si>
+    <t>0.0094,0.0005,0.9911,0.0001</t>
+  </si>
+  <si>
+    <t>0.2059,0.0013,0.8325,0.0011</t>
+  </si>
+  <si>
+    <t>0.3136,0.0024,0.6930,0.0079</t>
+  </si>
+  <si>
+    <t>0.9061,0.0006,0.0727,0.0014</t>
+  </si>
+  <si>
+    <t>0.9651,0.0007,0.0206,0.0001</t>
+  </si>
+  <si>
+    <t>0.9728,0.0012,0.0086,0.0002</t>
+  </si>
+  <si>
+    <t>0.9893,0.0042,0.0005,0.0021</t>
+  </si>
+  <si>
+    <t>0.9953,0.0014,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9973,0.0009,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9908,0.0042,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9960,0.0012,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9824,0.0111,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9873,0.0059,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9917,0.0040,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.2738,0.0024,0.7752,0.0009</t>
+  </si>
+  <si>
+    <t>0.0249,0.0008,0.9745,0.0003</t>
+  </si>
+  <si>
+    <t>0.3189,0.0055,0.7056,0.0065</t>
+  </si>
+  <si>
+    <t>0.7010,0.0056,0.3201,0.0026</t>
+  </si>
+  <si>
+    <t>0.2989,0.0003,0.7650,0.0009</t>
+  </si>
+  <si>
+    <t>0.8993,0.0005,0.0846,0.0012</t>
+  </si>
+  <si>
+    <t>0.6730,0.0014,0.3637,0.0026</t>
+  </si>
+  <si>
+    <t>0.6919,0.0008,0.2884,0.0050</t>
+  </si>
+  <si>
+    <t>0.9143,0.0025,0.0029,0.0414</t>
+  </si>
+  <si>
+    <t>0.0366,0.0014,0.0008,0.9846</t>
+  </si>
+  <si>
+    <t>0.0084,0.0007,0.0001,0.9976</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9255,0.0040,0.0019,0.0237</t>
+    <t>0.9802,0.0021,0.0016,0.0025</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1973,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2001,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2155,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2365,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2407,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2491,7 @@
         <v>259</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2505,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2575,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2925,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2967,7 @@
         <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3009,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3023,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3051,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3065,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3079,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3121,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3135,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>261</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3163,7 @@
         <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3611,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3706,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3835,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3849,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3877,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3919,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3947,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3975,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3989,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4154,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4378,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4605,7 @@
         <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4619,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4633,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4647,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4717,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4756,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4899,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5095,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5165,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5375,7 @@
         <v>259</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5403,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5417,7 @@
         <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5431,7 @@
         <v>259</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5459,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5473,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5487,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5501,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
